--- a/jogos_2025-06-10.xlsx
+++ b/jogos_2025-06-10.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G5" t="n">
